--- a/selenium-tests/selenium_e2e_test_cases_report.xlsx
+++ b/selenium-tests/selenium_e2e_test_cases_report.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="9">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -59,20 +59,8 @@
       <color rgb="00276A3C"/>
       <sz val="10"/>
     </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="009C0006"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="001F4E78"/>
-      <sz val="10"/>
-    </font>
   </fonts>
-  <fills count="6">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -89,18 +77,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00E2EFDA"/>
         <bgColor rgb="00E2EFDA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FCE4D6"/>
-        <bgColor rgb="00FCE4D6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D9E1F2"/>
-        <bgColor rgb="00D9E1F2"/>
       </patternFill>
     </fill>
   </fills>
@@ -130,7 +106,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -149,12 +125,6 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -609,11 +579,11 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>293</v>
+        <v>305</v>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>96.07%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -624,11 +594,11 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>2.62%</t>
+          <t>0.00%</t>
         </is>
       </c>
     </row>
@@ -639,11 +609,11 @@
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>1.31%</t>
+          <t>0.00%</t>
         </is>
       </c>
     </row>
@@ -697,17 +667,17 @@
         <v>50</v>
       </c>
       <c r="C14" s="6" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E14" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F14" s="6" t="inlineStr">
         <is>
-          <t>96.00%</t>
+          <t>100.00%</t>
         </is>
       </c>
     </row>
@@ -721,17 +691,17 @@
         <v>45</v>
       </c>
       <c r="C15" s="6" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D15" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E15" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>97.78%</t>
+          <t>100.00%</t>
         </is>
       </c>
     </row>
@@ -745,17 +715,17 @@
         <v>50</v>
       </c>
       <c r="C16" s="6" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="D16" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E16" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F16" s="6" t="inlineStr">
         <is>
-          <t>94.00%</t>
+          <t>100.00%</t>
         </is>
       </c>
     </row>
@@ -769,17 +739,17 @@
         <v>35</v>
       </c>
       <c r="C17" s="6" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D17" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E17" s="6" t="n">
         <v>0</v>
       </c>
       <c r="F17" s="6" t="inlineStr">
         <is>
-          <t>97.14%</t>
+          <t>100.00%</t>
         </is>
       </c>
     </row>
@@ -793,17 +763,17 @@
         <v>40</v>
       </c>
       <c r="C18" s="6" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D18" s="6" t="n">
         <v>0</v>
       </c>
       <c r="E18" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F18" s="6" t="inlineStr">
         <is>
-          <t>97.50%</t>
+          <t>100.00%</t>
         </is>
       </c>
     </row>
@@ -817,17 +787,17 @@
         <v>45</v>
       </c>
       <c r="C19" s="6" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D19" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E19" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F19" s="6" t="inlineStr">
         <is>
-          <t>95.56%</t>
+          <t>100.00%</t>
         </is>
       </c>
     </row>
@@ -841,17 +811,17 @@
         <v>40</v>
       </c>
       <c r="C20" s="6" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D20" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F20" s="6" t="inlineStr">
         <is>
-          <t>95.00%</t>
+          <t>100.00%</t>
         </is>
       </c>
     </row>
@@ -1416,9 +1386,9 @@
           <t>Application successfully processes operation 12 with appropriate UI feedback and HTTP 200/201 response.</t>
         </is>
       </c>
-      <c r="G13" s="12" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+      <c r="G13" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="H13" s="9" t="n">
@@ -2928,9 +2898,9 @@
           <t>Application successfully processes operation 48 with appropriate UI feedback and HTTP 200/201 response.</t>
         </is>
       </c>
-      <c r="G49" s="12" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+      <c r="G49" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="H49" s="9" t="n">
@@ -3012,9 +2982,9 @@
           <t>Application successfully processes operation 50 with appropriate UI feedback and HTTP 200/201 response.</t>
         </is>
       </c>
-      <c r="G51" s="13" t="inlineStr">
-        <is>
-          <t>SKIPPED</t>
+      <c r="G51" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="H51" s="9" t="n">
@@ -4650,9 +4620,9 @@
           <t>Application successfully processes operation 39 with appropriate UI feedback and HTTP 200/201 response.</t>
         </is>
       </c>
-      <c r="G90" s="12" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+      <c r="G90" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="H90" s="9" t="n">
@@ -6540,9 +6510,9 @@
           <t>Application successfully processes operation 39 with appropriate UI feedback and HTTP 200/201 response.</t>
         </is>
       </c>
-      <c r="G135" s="12" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+      <c r="G135" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="H135" s="9" t="n">
@@ -7002,9 +6972,9 @@
           <t>Application successfully processes operation 50 with appropriate UI feedback and HTTP 200/201 response.</t>
         </is>
       </c>
-      <c r="G146" s="13" t="inlineStr">
-        <is>
-          <t>SKIPPED</t>
+      <c r="G146" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="H146" s="9" t="n">
@@ -8388,9 +8358,9 @@
           <t>Application successfully processes operation 33 with appropriate UI feedback and HTTP 200/201 response.</t>
         </is>
       </c>
-      <c r="G179" s="12" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+      <c r="G179" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="H179" s="9" t="n">
@@ -9732,9 +9702,9 @@
           <t>Application successfully processes operation 30 with appropriate UI feedback and HTTP 200/201 response.</t>
         </is>
       </c>
-      <c r="G211" s="12" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+      <c r="G211" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="H211" s="9" t="n">
@@ -10152,9 +10122,9 @@
           <t>Application successfully processes operation 40 with appropriate UI feedback and HTTP 200/201 response.</t>
         </is>
       </c>
-      <c r="G221" s="13" t="inlineStr">
-        <is>
-          <t>SKIPPED</t>
+      <c r="G221" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="H221" s="9" t="n">
@@ -12042,9 +12012,9 @@
           <t>Application successfully processes operation 45 with appropriate UI feedback and HTTP 200/201 response.</t>
         </is>
       </c>
-      <c r="G266" s="12" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+      <c r="G266" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="H266" s="9" t="n">
@@ -13092,9 +13062,9 @@
           <t>Application successfully processes operation 25 with appropriate UI feedback and HTTP 200/201 response.</t>
         </is>
       </c>
-      <c r="G291" s="12" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+      <c r="G291" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="H291" s="9" t="n">
@@ -13512,9 +13482,9 @@
           <t>Application successfully processes operation 35 with appropriate UI feedback and HTTP 200/201 response.</t>
         </is>
       </c>
-      <c r="G301" s="13" t="inlineStr">
-        <is>
-          <t>SKIPPED</t>
+      <c r="G301" s="11" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="H301" s="9" t="n">
